--- a/v5frhmlitisu/dateien/PhysioNebenbei-Werkzeuge.xlsx
+++ b/v5frhmlitisu/dateien/PhysioNebenbei-Werkzeuge.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +83,26 @@
       <color rgb="0056645D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0F6B5C"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0F6B5C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF0F6B5C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +122,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCEAE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F0EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -181,6 +204,29 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,7 +655,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>PhysioNebenbei — Werkzeuge zum Rechnen</t>
         </is>
@@ -654,7 +700,7 @@
     </row>
     <row r="9" ht="16" customHeight="1"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Gelb hinterlegte Zellen sind zum Ausfüllen gedacht.</t>
         </is>
@@ -670,7 +716,7 @@
     <row r="12" ht="16" customHeight="1"/>
     <row r="13" ht="16" customHeight="1"/>
     <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Wichtig, damit hier keine Missverständnisse entstehen</t>
         </is>
@@ -728,14 +774,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Preis-Kalkulation</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>1 · Was muss ich verlangen?</t>
         </is>
@@ -748,13 +795,14 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Gewünschtes Nebeneinkommen pro Monat (netto)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="26" t="n">
         <v>500</v>
       </c>
     </row>
@@ -764,7 +812,7 @@
           <t>Geschätzter Grenzsteuersatz</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="27" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -774,7 +822,7 @@
           <t>Jährliche Fixkosten (Berufshaftpflicht, Fortbildung, Material)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="26" t="n">
         <v>250</v>
       </c>
     </row>
@@ -784,7 +832,7 @@
           <t>Behandlungsdauer inkl. Fahrtzeit (Minuten)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="28" t="n">
         <v>60</v>
       </c>
     </row>
@@ -794,10 +842,11 @@
           <t>Verfügbare Stunden pro Woche</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="29" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
@@ -843,18 +892,20 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>→ Nötiger Preis pro Behandlung</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="31">
         <f>B14/B15</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>2 · Was bleibt mir bei meinem geplanten Preis?</t>
         </is>
@@ -867,13 +918,14 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Dein geplanter Preis pro Behandlung</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="26" t="n">
         <v>70</v>
       </c>
     </row>
@@ -883,10 +935,11 @@
           <t>Geplante Behandlungen pro Monat</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="28" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
@@ -910,12 +963,12 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>→ Netto pro Monat, nach Steuer-Rücklage</t>
         </is>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="31">
         <f>B26*(1-B7)</f>
         <v/>
       </c>
@@ -944,14 +997,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Steuer-Rücklage</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Betriebsausgaben im Jahr</t>
         </is>
@@ -963,7 +1017,7 @@
           <t>Berufshaftpflicht</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="26" t="n">
         <v>120</v>
       </c>
     </row>
@@ -973,7 +1027,7 @@
           <t>Fahrtkosten</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="26" t="n">
         <v>300</v>
       </c>
     </row>
@@ -983,7 +1037,7 @@
           <t>Material / Verbrauchsmaterial</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="26" t="n">
         <v>150</v>
       </c>
     </row>
@@ -993,7 +1047,7 @@
           <t>Fortbildung</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="26" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1003,7 +1057,7 @@
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1018,8 +1072,9 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Einnahmen und Gewinn</t>
         </is>
@@ -1031,7 +1086,7 @@
           <t>Einnahmen im Jahr</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="26" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -1046,8 +1101,9 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Steuer-Rücklage</t>
         </is>
@@ -1059,7 +1115,7 @@
           <t>Geschätzter Grenzsteuersatz</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="27" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -1069,7 +1125,7 @@
           <t>Sicherheitspuffer</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="27" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1085,23 +1141,23 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>→ Empfohlene Rücklage</t>
         </is>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="31">
         <f>B13*(B16+B17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>→ Voraussichtliches Netto nach Rücklage</t>
         </is>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="31">
         <f>B13-B19</f>
         <v/>
       </c>
@@ -1136,7 +1192,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>EÜR — Einnahmen-Überschuss-Rechnung</t>
         </is>
@@ -1149,6 +1205,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -1202,22 +1259,22 @@
           <t>Januar</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19" t="n">
+      <c r="B5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="12">
@@ -1235,22 +1292,22 @@
           <t>Februar</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="19" t="n">
+      <c r="B6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="12">
@@ -1268,22 +1325,22 @@
           <t>März</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19" t="n">
+      <c r="B7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="12">
@@ -1301,22 +1358,22 @@
           <t>April</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="19" t="n">
+      <c r="B8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="12">
@@ -1334,22 +1391,22 @@
           <t>Mai</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19" t="n">
+      <c r="B9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="12">
@@ -1367,22 +1424,22 @@
           <t>Juni</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="19" t="n">
+      <c r="B10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="12">
@@ -1400,22 +1457,22 @@
           <t>Juli</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19" t="n">
+      <c r="B11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12">
@@ -1433,22 +1490,22 @@
           <t>August</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="19" t="n">
+      <c r="B12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12">
@@ -1466,22 +1523,22 @@
           <t>September</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19" t="n">
+      <c r="B13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="12">
@@ -1499,22 +1556,22 @@
           <t>Oktober</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="19" t="n">
+      <c r="B14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="12">
@@ -1532,22 +1589,22 @@
           <t>November</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="19" t="n">
+      <c r="B15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="12">
@@ -1565,22 +1622,22 @@
           <t>Dezember</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="19" t="n">
+      <c r="B16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="12">
@@ -1593,7 +1650,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Jahressumme</t>
         </is>
@@ -1658,7 +1715,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Behandlungsdokumentation</t>
         </is>
@@ -1671,6 +1728,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>

--- a/v5frhmlitisu/dateien/PhysioNebenbei-Werkzeuge.xlsx
+++ b/v5frhmlitisu/dateien/PhysioNebenbei-Werkzeuge.xlsx
@@ -86,19 +86,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF0F6B5C"/>
+      <color rgb="FF2F35E8"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF0F6B5C"/>
+      <color rgb="FF2F35E8"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF0F6B5C"/>
+      <color rgb="FF2F35E8"/>
       <sz val="10"/>
     </font>
   </fonts>
